--- a/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-26T08:53:51+00:00</t>
+    <t>2026-03-27T13:44:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T13:44:47+00:00</t>
+    <t>2026-03-27T15:26:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T15:26:56+00:00</t>
+    <t>2026-04-06T22:23:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-06T22:23:09+00:00</t>
+    <t>2026-04-07T07:24:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T07:24:51+00:00</t>
+    <t>2026-04-07T09:57:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T09:57:16+00:00</t>
+    <t>2026-04-07T13:26:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T13:26:48+00:00</t>
+    <t>2026-04-09T11:21:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T11:21:19+00:00</t>
+    <t>2026-04-12T21:17:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-12T21:17:41+00:00</t>
+    <t>2026-04-13T07:14:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T07:14:32+00:00</t>
+    <t>2026-04-13T09:32:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:32:15+00:00</t>
+    <t>2026-04-13T12:28:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T12:28:33+00:00</t>
+    <t>2026-04-13T15:14:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T09:34:44+00:00</t>
+    <t>2026-04-15T07:18:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:18:39+00:00</t>
+    <t>2026-04-16T13:50:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T13:50:37+00:00</t>
+    <t>2026-04-16T14:02:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T14:02:18+00:00</t>
+    <t>2026-04-20T12:06:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T12:06:43+00:00</t>
+    <t>2026-04-27T11:36:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-27T11:36:28+00:00</t>
+    <t>2026-05-06T21:36:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T21:36:32+00:00</t>
+    <t>2026-05-07T10:57:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T10:57:29+00:00</t>
+    <t>2026-05-08T13:10:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T13:10:44+00:00</t>
+    <t>2026-05-12T09:48:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T09:48:56+00:00</t>
+    <t>2026-05-12T14:15:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T14:15:33+00:00</t>
+    <t>2026-05-15T11:07:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/develop/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T11:07:33+00:00</t>
+    <t>2026-05-19T15:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
